--- a/public/templates/FMAC-Monthly-Plan-Template.xlsx
+++ b/public/templates/FMAC-Monthly-Plan-Template.xlsx
@@ -54,12 +54,15 @@
     <comment ref="J3" authorId="0">
       <text/>
     </comment>
+    <comment ref="K3" authorId="0">
+      <text/>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="88">
   <si>
     <t>قالب الخطة الشهرية — اقرأ هذه الصفحة أوّلاً</t>
   </si>
@@ -157,6 +160,12 @@
     <t>البطولة القادمة</t>
   </si>
   <si>
+    <t>إجراءات الاستشفاء</t>
+  </si>
+  <si>
+    <t>إجراءات السلامة والوقاية</t>
+  </si>
+  <si>
     <t>مثال: الشهر ⇐ سبتمبر 2026 · الفئة ⇐ ناشئين تحت 15 · مرحلة الموسم ⇐ إعداد عام.</t>
   </si>
   <si>
@@ -247,6 +256,9 @@
     <t>الراحة (د)</t>
   </si>
   <si>
+    <t>نوع المحتوى</t>
+  </si>
+  <si>
     <t>الأحد</t>
   </si>
   <si>
@@ -262,6 +274,9 @@
     <t>حركية ورفع نبض · أوكيمي</t>
   </si>
   <si>
+    <t>بدني</t>
+  </si>
+  <si>
     <t>الجزء الرئيسي</t>
   </si>
   <si>
@@ -271,10 +286,16 @@
     <t>4×10</t>
   </si>
   <si>
+    <t>فني</t>
+  </si>
+  <si>
     <t>التهدئة</t>
   </si>
   <si>
     <t>تنفّس وتمطيط</t>
+  </si>
+  <si>
+    <t>نفسي</t>
   </si>
   <si>
     <t>مؤشرات القياس والاختبارات</t>
@@ -877,7 +898,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -962,16 +983,32 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -991,7 +1028,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -999,30 +1036,30 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1139,7 +1176,7 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1168,7 +1205,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1176,30 +1213,30 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1260,7 +1297,7 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1278,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1288,11 +1325,12 @@
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1303,60 +1341,64 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" s="10">
         <v>18</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>24</v>
@@ -1367,31 +1409,34 @@
       <c r="J4" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F5" s="10">
         <v>67</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I5" s="10">
         <v>7</v>
@@ -1399,28 +1444,31 @@
       <c r="J5" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F6" s="10">
         <v>10</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>24</v>
@@ -1431,8 +1479,11 @@
       <c r="J6" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>24</v>
       </c>
@@ -1463,8 +1514,11 @@
       <c r="J7" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
@@ -1495,8 +1549,11 @@
       <c r="J8" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
@@ -1527,8 +1584,11 @@
       <c r="J9" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>24</v>
       </c>
@@ -1559,8 +1619,11 @@
       <c r="J10" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>24</v>
       </c>
@@ -1591,8 +1654,11 @@
       <c r="J11" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
@@ -1623,8 +1689,11 @@
       <c r="J12" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>24</v>
       </c>
@@ -1655,8 +1724,11 @@
       <c r="J13" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>24</v>
       </c>
@@ -1687,8 +1759,11 @@
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>24</v>
       </c>
@@ -1719,8 +1794,11 @@
       <c r="J15" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>24</v>
       </c>
@@ -1751,8 +1829,11 @@
       <c r="J16" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>24</v>
       </c>
@@ -1783,8 +1864,11 @@
       <c r="J17" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>24</v>
       </c>
@@ -1815,8 +1899,11 @@
       <c r="J18" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>24</v>
       </c>
@@ -1847,8 +1934,11 @@
       <c r="J19" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>24</v>
       </c>
@@ -1879,8 +1969,11 @@
       <c r="J20" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>24</v>
       </c>
@@ -1911,8 +2004,11 @@
       <c r="J21" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>24</v>
       </c>
@@ -1943,8 +2039,11 @@
       <c r="J22" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>24</v>
       </c>
@@ -1975,8 +2074,11 @@
       <c r="J23" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>24</v>
       </c>
@@ -2007,8 +2109,11 @@
       <c r="J24" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
@@ -2039,8 +2144,11 @@
       <c r="J25" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>24</v>
       </c>
@@ -2071,8 +2179,11 @@
       <c r="J26" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>24</v>
       </c>
@@ -2103,8 +2214,11 @@
       <c r="J27" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>24</v>
       </c>
@@ -2135,8 +2249,11 @@
       <c r="J28" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>24</v>
       </c>
@@ -2167,8 +2284,11 @@
       <c r="J29" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>24</v>
       </c>
@@ -2199,8 +2319,11 @@
       <c r="J30" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>24</v>
       </c>
@@ -2231,8 +2354,11 @@
       <c r="J31" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>24</v>
       </c>
@@ -2263,8 +2389,11 @@
       <c r="J32" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>24</v>
       </c>
@@ -2295,8 +2424,11 @@
       <c r="J33" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>24</v>
       </c>
@@ -2327,8 +2459,11 @@
       <c r="J34" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>24</v>
       </c>
@@ -2359,8 +2494,11 @@
       <c r="J35" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>24</v>
       </c>
@@ -2391,8 +2529,11 @@
       <c r="J36" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
@@ -2423,8 +2564,11 @@
       <c r="J37" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>24</v>
       </c>
@@ -2455,8 +2599,11 @@
       <c r="J38" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>24</v>
       </c>
@@ -2487,8 +2634,11 @@
       <c r="J39" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>24</v>
       </c>
@@ -2519,8 +2669,11 @@
       <c r="J40" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>24</v>
       </c>
@@ -2551,8 +2704,11 @@
       <c r="J41" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>24</v>
       </c>
@@ -2583,8 +2739,11 @@
       <c r="J42" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>24</v>
       </c>
@@ -2615,8 +2774,11 @@
       <c r="J43" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>24</v>
       </c>
@@ -2647,8 +2809,11 @@
       <c r="J44" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>24</v>
       </c>
@@ -2679,8 +2844,11 @@
       <c r="J45" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>24</v>
       </c>
@@ -2711,8 +2879,11 @@
       <c r="J46" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>24</v>
       </c>
@@ -2743,8 +2914,11 @@
       <c r="J47" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K47" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>24</v>
       </c>
@@ -2775,8 +2949,11 @@
       <c r="J48" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K48" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>24</v>
       </c>
@@ -2807,8 +2984,11 @@
       <c r="J49" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K49" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>24</v>
       </c>
@@ -2839,8 +3019,11 @@
       <c r="J50" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K50" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>24</v>
       </c>
@@ -2871,8 +3054,11 @@
       <c r="J51" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K51" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>24</v>
       </c>
@@ -2903,8 +3089,11 @@
       <c r="J52" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>24</v>
       </c>
@@ -2935,8 +3124,11 @@
       <c r="J53" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>24</v>
       </c>
@@ -2967,8 +3159,11 @@
       <c r="J54" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K54" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>24</v>
       </c>
@@ -2999,8 +3194,11 @@
       <c r="J55" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K55" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>24</v>
       </c>
@@ -3031,8 +3229,11 @@
       <c r="J56" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>24</v>
       </c>
@@ -3063,8 +3264,11 @@
       <c r="J57" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>24</v>
       </c>
@@ -3095,8 +3299,11 @@
       <c r="J58" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>24</v>
       </c>
@@ -3127,8 +3334,11 @@
       <c r="J59" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>24</v>
       </c>
@@ -3159,8 +3369,11 @@
       <c r="J60" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>24</v>
       </c>
@@ -3191,8 +3404,11 @@
       <c r="J61" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>24</v>
       </c>
@@ -3223,8 +3439,11 @@
       <c r="J62" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>24</v>
       </c>
@@ -3255,8 +3474,11 @@
       <c r="J63" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
         <v>24</v>
       </c>
@@ -3287,8 +3509,11 @@
       <c r="J64" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K64" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>24</v>
       </c>
@@ -3319,8 +3544,11 @@
       <c r="J65" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K65" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>24</v>
       </c>
@@ -3351,8 +3579,11 @@
       <c r="J66" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K66" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>24</v>
       </c>
@@ -3383,8 +3614,11 @@
       <c r="J67" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K67" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>24</v>
       </c>
@@ -3415,8 +3649,11 @@
       <c r="J68" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K68" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>24</v>
       </c>
@@ -3447,8 +3684,11 @@
       <c r="J69" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K69" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>24</v>
       </c>
@@ -3479,8 +3719,11 @@
       <c r="J70" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K70" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>24</v>
       </c>
@@ -3511,8 +3754,11 @@
       <c r="J71" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K71" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>24</v>
       </c>
@@ -3543,8 +3789,11 @@
       <c r="J72" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K72" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>24</v>
       </c>
@@ -3575,8 +3824,11 @@
       <c r="J73" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K73" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>24</v>
       </c>
@@ -3607,8 +3859,11 @@
       <c r="J74" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K74" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>24</v>
       </c>
@@ -3639,8 +3894,11 @@
       <c r="J75" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K75" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>24</v>
       </c>
@@ -3671,8 +3929,11 @@
       <c r="J76" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K76" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>24</v>
       </c>
@@ -3703,8 +3964,11 @@
       <c r="J77" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K77" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>24</v>
       </c>
@@ -3735,8 +3999,11 @@
       <c r="J78" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K78" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>24</v>
       </c>
@@ -3767,8 +4034,11 @@
       <c r="J79" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K79" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>24</v>
       </c>
@@ -3799,8 +4069,11 @@
       <c r="J80" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K80" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>24</v>
       </c>
@@ -3831,8 +4104,11 @@
       <c r="J81" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K81" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
         <v>24</v>
       </c>
@@ -3863,8 +4139,11 @@
       <c r="J82" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K82" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>24</v>
       </c>
@@ -3895,8 +4174,11 @@
       <c r="J83" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K83" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>24</v>
       </c>
@@ -3927,8 +4209,11 @@
       <c r="J84" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K84" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>24</v>
       </c>
@@ -3959,8 +4244,11 @@
       <c r="J85" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K85" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>24</v>
       </c>
@@ -3991,8 +4279,11 @@
       <c r="J86" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K86" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>24</v>
       </c>
@@ -4023,8 +4314,11 @@
       <c r="J87" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K87" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>24</v>
       </c>
@@ -4055,8 +4349,11 @@
       <c r="J88" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K88" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>24</v>
       </c>
@@ -4087,8 +4384,11 @@
       <c r="J89" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K89" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>24</v>
       </c>
@@ -4119,8 +4419,11 @@
       <c r="J90" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K90" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>24</v>
       </c>
@@ -4151,8 +4454,11 @@
       <c r="J91" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K91" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>24</v>
       </c>
@@ -4183,8 +4489,11 @@
       <c r="J92" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K92" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>24</v>
       </c>
@@ -4215,8 +4524,11 @@
       <c r="J93" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K93" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>24</v>
       </c>
@@ -4247,8 +4559,11 @@
       <c r="J94" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K94" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>24</v>
       </c>
@@ -4279,8 +4594,11 @@
       <c r="J95" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K95" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>24</v>
       </c>
@@ -4311,8 +4629,11 @@
       <c r="J96" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K96" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>24</v>
       </c>
@@ -4343,8 +4664,11 @@
       <c r="J97" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K97" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>24</v>
       </c>
@@ -4375,8 +4699,11 @@
       <c r="J98" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K98" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>24</v>
       </c>
@@ -4407,8 +4734,11 @@
       <c r="J99" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K99" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>24</v>
       </c>
@@ -4439,8 +4769,11 @@
       <c r="J100" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K100" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>24</v>
       </c>
@@ -4471,8 +4804,11 @@
       <c r="J101" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K101" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
         <v>24</v>
       </c>
@@ -4503,8 +4839,11 @@
       <c r="J102" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K102" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>24</v>
       </c>
@@ -4535,8 +4874,11 @@
       <c r="J103" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K103" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>24</v>
       </c>
@@ -4567,8 +4909,11 @@
       <c r="J104" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K104" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>24</v>
       </c>
@@ -4599,8 +4944,11 @@
       <c r="J105" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K105" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
         <v>24</v>
       </c>
@@ -4631,8 +4979,11 @@
       <c r="J106" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K106" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>24</v>
       </c>
@@ -4663,8 +5014,11 @@
       <c r="J107" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K107" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>24</v>
       </c>
@@ -4695,8 +5049,11 @@
       <c r="J108" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K108" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>24</v>
       </c>
@@ -4727,8 +5084,11 @@
       <c r="J109" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K109" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>24</v>
       </c>
@@ -4759,8 +5119,11 @@
       <c r="J110" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K110" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>24</v>
       </c>
@@ -4791,8 +5154,11 @@
       <c r="J111" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K111" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>24</v>
       </c>
@@ -4823,8 +5189,11 @@
       <c r="J112" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K112" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>24</v>
       </c>
@@ -4855,8 +5224,11 @@
       <c r="J113" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K113" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>24</v>
       </c>
@@ -4887,8 +5259,11 @@
       <c r="J114" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K114" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>24</v>
       </c>
@@ -4919,8 +5294,11 @@
       <c r="J115" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K115" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>24</v>
       </c>
@@ -4951,8 +5329,11 @@
       <c r="J116" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K116" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>24</v>
       </c>
@@ -4983,8 +5364,11 @@
       <c r="J117" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K117" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>24</v>
       </c>
@@ -5015,8 +5399,11 @@
       <c r="J118" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K118" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>24</v>
       </c>
@@ -5047,8 +5434,11 @@
       <c r="J119" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K119" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>24</v>
       </c>
@@ -5079,8 +5469,11 @@
       <c r="J120" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K120" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>24</v>
       </c>
@@ -5111,8 +5504,11 @@
       <c r="J121" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K121" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>24</v>
       </c>
@@ -5143,8 +5539,11 @@
       <c r="J122" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K122" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>24</v>
       </c>
@@ -5175,8 +5574,11 @@
       <c r="J123" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K123" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>24</v>
       </c>
@@ -5207,8 +5609,11 @@
       <c r="J124" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K124" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>24</v>
       </c>
@@ -5239,8 +5644,11 @@
       <c r="J125" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K125" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>24</v>
       </c>
@@ -5271,12 +5679,27 @@
       <c r="J126" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
+      <c r="K126" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="11:11" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="11:11" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="11:11" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="11:11" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:J3"/>
+  <autoFilter ref="A3:K3"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="اختر من: فني · بدني · خططي · نفسي" sqref="K10:K130">
+      <formula1>"فني,بدني,خططي,نفسي"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="اختر من: فني · بدني · خططي · نفسي" sqref="K4:K130">
+      <formula1>"فني,بدني,خططي,نفسي"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -5296,7 +5719,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5305,36 +5728,36 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5475,7 +5898,7 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
